--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v2.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v2.xlsx
@@ -167,7 +167,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">기</t>
+      <t xml:space="preserve">분할체</t>
     </r>
     <r>
       <rPr>
@@ -178,7 +178,28 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(48TON, 38TON) </t>
+      <t xml:space="preserve">(35TON </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개구부 측</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 48TON) </t>
     </r>
     <r>
       <rPr>
@@ -1563,7 +1584,35 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">240</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 원</t>
     </r>
   </si>
   <si>
@@ -1615,7 +1664,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">탠덤 회전</t>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">170</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 원</t>
     </r>
   </si>
   <si>
@@ -4650,11 +4718,11 @@
         <v>1</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>2300000</v>
+        <v>2400000</v>
       </c>
       <c r="H13" s="13" t="n">
         <f aca="false">F13*G13</f>
-        <v>2300000</v>
+        <v>2400000</v>
       </c>
       <c r="I13" s="23" t="s">
         <v>46</v>
@@ -4818,11 +4886,11 @@
         <v>1</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>807450</v>
+        <v>707450</v>
       </c>
       <c r="H20" s="13" t="n">
         <f aca="false">F20*G20</f>
-        <v>807450</v>
+        <v>707450</v>
       </c>
       <c r="I20" s="23" t="s">
         <v>63</v>

--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v2.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="136">
   <si>
     <t xml:space="preserve">견      적      서</t>
   </si>
@@ -2312,6 +2312,138 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">장비 대여</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CO2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용접기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대당 일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 원</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">장비사용료</t>
   </si>
   <si>
@@ -2322,6 +2454,472 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">그라인더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">환기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조명</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">재료비</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CO2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">와이어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디스크</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">비파괴검사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PT/UT</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요구 시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">범위 확인 필요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">도장 보수</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">용접부</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  작업 내용</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사다리형 일체 베이스 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10,000×5,000×H800 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제작</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설치 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">제작작업</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강재 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H-250·H-200·H-150·H-125</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">KG</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자재산출 시트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">손실 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">포함</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">제작 기공</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">방청 도장</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프라이머 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">㎡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">자재산출 시트 도장면적</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">용접기</t>
     </r>
     <r>
@@ -2341,7 +2939,21 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">그라인더</t>
+      <t xml:space="preserve">절단기</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">소모품</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용접봉</t>
     </r>
     <r>
       <rPr>
@@ -2360,21 +2972,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">환기</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">재료비</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">용접봉</t>
+      <t xml:space="preserve">가스</t>
     </r>
     <r>
       <rPr>
@@ -2393,415 +2991,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">디스크</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">비파괴검사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT/UT</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요구 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">범위 확인 필요</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방청</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">도장 보수</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">용접부</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  작업 내용</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사다리형 일체 베이스 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10,000×5,000×H800 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제작</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">설치 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(4</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">제작작업</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">강재 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H-250·H-200·H-150·H-125</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">KG</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자재산출 시트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">손실 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">포함</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">제작 기공</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">방청 도장</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">프라이머 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">㎡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">자재산출 시트 도장면적</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">용접기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">절단기</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">소모품</t>
   </si>
   <si>
     <t xml:space="preserve">슬라이딩면 처리</t>
@@ -4350,7 +4541,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="12" t="n">
-        <f aca="false">용접!H24</f>
+        <f aca="false">용접!H25</f>
         <v>25000000</v>
       </c>
       <c r="H13" s="13" t="n">
@@ -5006,7 +5197,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.4"/>
@@ -5252,45 +5443,47 @@
       <c r="C16" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>51</v>
+      <c r="E16" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>2500000</v>
+        <v>400000</v>
       </c>
       <c r="H16" s="13" t="n">
         <f aca="false">F16*G16</f>
-        <v>2500000</v>
-      </c>
-      <c r="I16" s="23"/>
+        <v>3600000</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>17</v>
+        <v>83</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="F17" s="21" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>3000000</v>
+        <v>800000</v>
       </c>
       <c r="H17" s="13" t="n">
         <f aca="false">F17*G17</f>
-        <v>3000000</v>
+        <v>800000</v>
       </c>
       <c r="I17" s="23"/>
     </row>
@@ -5298,10 +5491,10 @@
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>17</v>
@@ -5310,24 +5503,22 @@
         <v>1</v>
       </c>
       <c r="G18" s="22" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="H18" s="13" t="n">
         <f aca="false">F18*G18</f>
-        <v>2500000</v>
-      </c>
-      <c r="I18" s="23" t="s">
-        <v>84</v>
-      </c>
+        <v>3000000</v>
+      </c>
+      <c r="I18" s="23"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" s="11" t="s">
         <v>86</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>17</v>
@@ -5336,134 +5527,147 @@
         <v>1</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>1500000</v>
+        <v>2500000</v>
       </c>
       <c r="H19" s="13" t="n">
         <f aca="false">F19*G19</f>
-        <v>1500000</v>
-      </c>
-      <c r="I19" s="23"/>
+        <v>2500000</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
-        <v>57</v>
-      </c>
+      <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="10" t="s">
-        <v>56</v>
+        <v>89</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>600000</v>
+        <v>1500000</v>
       </c>
       <c r="H20" s="13" t="n">
         <f aca="false">F20*G20</f>
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="I20" s="23"/>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11"/>
+      <c r="A21" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F21" s="24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G21" s="13"/>
+        <v>56</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" s="22" t="n">
+        <v>600000</v>
+      </c>
       <c r="H21" s="13" t="n">
-        <f aca="false">(H11+H12+H13+H14+H15)*0.033</f>
-        <v>308550</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>61</v>
-      </c>
+        <f aca="false">F21*G21</f>
+        <v>3000000</v>
+      </c>
+      <c r="I21" s="23"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
       <c r="C22" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13" t="n">
+        <f aca="false">(H11+H12+H13+H14+H15)*0.033</f>
+        <v>308550</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11" t="s">
+      <c r="D23" s="11"/>
+      <c r="E23" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="21" t="n">
+      <c r="F23" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="22" t="n">
-        <v>2841450</v>
-      </c>
-      <c r="H22" s="13" t="n">
-        <f aca="false">F22*G22</f>
-        <v>2841450</v>
-      </c>
-      <c r="I22" s="23" t="s">
+      <c r="G23" s="22" t="n">
+        <v>941450</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <f aca="false">F23*G23</f>
+        <v>941450</v>
+      </c>
+      <c r="I23" s="23" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="9" t="s">
+    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="16" t="n">
-        <f aca="false">SUM(H11:H22)</f>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="16" t="n">
+        <f aca="false">SUM(H11:H23)</f>
         <v>25000000</v>
       </c>
-      <c r="I23" s="17"/>
-    </row>
-    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
+      <c r="I24" s="17"/>
+    </row>
+    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="15" t="s">
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="16" t="n">
-        <f aca="false">H23</f>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="16" t="n">
+        <f aca="false">H24</f>
         <v>25000000</v>
       </c>
-      <c r="I24" s="17"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
+      <c r="I25" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -5476,7 +5680,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -5487,8 +5691,21 @@
       <c r="H28" s="20"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="26" t="s">
+    <row r="29" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="26" t="s">
         <v>65</v>
       </c>
     </row>
@@ -5503,13 +5720,13 @@
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:B12"/>
     <mergeCell ref="A13:B14"/>
-    <mergeCell ref="A15:B19"/>
-    <mergeCell ref="A20:B22"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A15:B20"/>
+    <mergeCell ref="A21:B23"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:G25"/>
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A29:I29"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5594,7 +5811,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -5632,17 +5849,17 @@
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F11" s="21" t="n">
         <v>3227</v>
@@ -5655,7 +5872,7 @@
         <v>4195100</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5665,7 +5882,7 @@
         <v>37</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>39</v>
@@ -5681,20 +5898,20 @@
         <v>3600000</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F13" s="21" t="n">
         <v>102</v>
@@ -5707,17 +5924,17 @@
         <v>1530000</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>51</v>
@@ -5738,10 +5955,10 @@
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>17</v>
@@ -5762,10 +5979,10 @@
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>17</v>
@@ -5781,17 +5998,17 @@
         <v>800000</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>45</v>
@@ -5814,7 +6031,7 @@
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11" t="s">
@@ -5831,7 +6048,7 @@
         <v>1500000</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6022,56 +6239,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C4" s="30"/>
       <c r="D4" s="30"/>
@@ -6087,10 +6304,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="29" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
@@ -6106,10 +6323,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
@@ -6125,10 +6342,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
@@ -6144,10 +6361,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
@@ -6163,7 +6380,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v2.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v2.xlsx
@@ -12,7 +12,8 @@
     <sheet name="도비" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="용접" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="베이스" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="공정표" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="베이스자재" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="공정표" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="149">
   <si>
     <t xml:space="preserve">견      적      서</t>
   </si>
@@ -1126,7 +1127,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">베이스 강재는 개략 산출</t>
+      <t xml:space="preserve">베이스 </t>
     </r>
     <r>
       <rPr>
@@ -1136,7 +1137,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">H</t>
     </r>
     <r>
       <rPr>
@@ -1145,7 +1146,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">약 </t>
+      <t xml:space="preserve">빔은 중고품 기준입니다</t>
     </r>
     <r>
       <rPr>
@@ -1155,7 +1156,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3.2</t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -1164,7 +1165,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">톤</t>
+      <t xml:space="preserve">신품 적용 시 </t>
     </r>
     <r>
       <rPr>
@@ -1174,7 +1175,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">3,997,657</t>
     </r>
     <r>
       <rPr>
@@ -1183,7 +1184,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이며 구조검토 결과에 따라 변경될 수 있습니다</t>
+      <t xml:space="preserve">원이 추가됩니다</t>
     </r>
     <r>
       <rPr>
@@ -2656,7 +2657,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">사다리형 일체 베이스 </t>
+      <t xml:space="preserve">사다리형 일체 베이스 제작</t>
     </r>
     <r>
       <rPr>
@@ -2667,7 +2668,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">10,000×5,000×H800 </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -2677,7 +2678,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제작</t>
+      <t xml:space="preserve">설치</t>
     </r>
     <r>
       <rPr>
@@ -2688,33 +2689,239 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">, H-250×250 (4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">자재</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빔 구매 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">H-250×250, 10m 4EA·5m 16EA·0.6m 30EA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급처 견적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">신품 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13,575,440</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">운임</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빔 운반</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">공급처 견적</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지 게 차</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자재 하역</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">설치 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(4</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조립</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제작작업</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제작 기공</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
@@ -2723,8 +2930,7 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
@@ -2734,18 +2940,210 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">일</t>
     </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용접기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">절단기</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">소모품</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용접봉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디스크</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">슬라이딩면 처리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그리스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·PTFE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시트</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">밀착 이동용 레일 상면</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">베이스 자재</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: H</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빔 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H-250×250×9×14 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급처 견적</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부가세 미포함</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
@@ -2755,118 +3153,289 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">제작작업</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">강재 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H-250·H-200·H-150·H-125</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">KG</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자재산출 시트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">손실 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">포함</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">제작 기공</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">길이</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수량</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(EA)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">총 길이</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단위중량</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(kg/m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중량</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(kg)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">합계</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금액</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">kg</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">당</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">신품</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중고 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">견적 반영</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지게차 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2874,58 +3443,79 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">방청 도장</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">프라이머 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">㎡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">자재산출 시트 도장면적</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">용접기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
+    <t xml:space="preserve">신품 차액</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단위중량 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">72.4 kg/m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KS H-250×250×9×14 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공칭값이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -2934,185 +3524,22 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">절단기</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">소모품</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">용접봉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">디스크</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">슬라이딩면 처리</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그리스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·PTFE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시트</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">밀착 이동용 레일 상면</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화 물 차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">운반</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구조검토</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제작도</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">레일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기둥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지반 지지력</t>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금액은 사용자가 받은 공급처 견적이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
   </si>
   <si>
@@ -3778,13 +4205,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="168" formatCode="General"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3919,6 +4347,27 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="WenQuanYi Zen Hei"/>
@@ -4000,7 +4449,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4113,6 +4562,58 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4122,10 +4623,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4568,7 +5065,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="12" t="n">
-        <f aca="false">베이스!H23</f>
+        <f aca="false">베이스!H22</f>
         <v>18000000</v>
       </c>
       <c r="H14" s="13" t="n">
@@ -5743,7 +6240,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.4"/>
@@ -5852,24 +6349,24 @@
         <v>92</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="10" t="s">
         <v>94</v>
       </c>
+      <c r="E11" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="F11" s="21" t="n">
-        <v>3227</v>
+        <v>1</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>1300</v>
+        <v>9577783</v>
       </c>
       <c r="H11" s="13" t="n">
         <f aca="false">F11*G11</f>
-        <v>4195100</v>
+        <v>9577783</v>
       </c>
       <c r="I11" s="23" t="s">
         <v>95</v>
@@ -5879,99 +6376,101 @@
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>39</v>
+      <c r="D12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>300000</v>
+        <v>160000</v>
       </c>
       <c r="H12" s="13" t="n">
         <f aca="false">F12*G12</f>
-        <v>3600000</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>97</v>
+        <v>160000</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>15000</v>
+        <v>300000</v>
       </c>
       <c r="H13" s="13" t="n">
         <f aca="false">F13*G13</f>
-        <v>1530000</v>
-      </c>
-      <c r="I13" s="23" t="s">
-        <v>101</v>
-      </c>
+        <v>600000</v>
+      </c>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11"/>
+      <c r="A14" s="11" t="s">
+        <v>102</v>
+      </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>1500000</v>
+        <v>300000</v>
       </c>
       <c r="H14" s="13" t="n">
         <f aca="false">F14*G14</f>
-        <v>1500000</v>
-      </c>
-      <c r="I14" s="23"/>
+        <v>3600000</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>17</v>
+        <v>105</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="F15" s="21" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="H15" s="13" t="n">
         <f aca="false">F15*G15</f>
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="I15" s="23"/>
     </row>
@@ -5979,10 +6478,10 @@
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>17</v>
@@ -5991,15 +6490,13 @@
         <v>1</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>800000</v>
+        <v>1000000</v>
       </c>
       <c r="H16" s="13" t="n">
         <f aca="false">F16*G16</f>
-        <v>800000</v>
-      </c>
-      <c r="I16" s="23" t="s">
-        <v>107</v>
-      </c>
+        <v>1000000</v>
+      </c>
+      <c r="I16" s="23"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11"/>
@@ -6011,7 +6508,7 @@
         <v>109</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F17" s="21" t="n">
         <v>1</v>
@@ -6023,7 +6520,9 @@
         <f aca="false">F17*G17</f>
         <v>500000</v>
       </c>
-      <c r="I17" s="23"/>
+      <c r="I17" s="23" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
@@ -6031,131 +6530,120 @@
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="D18" s="11"/>
-      <c r="E18" s="11" t="s">
-        <v>17</v>
+      <c r="E18" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" s="22" t="n">
-        <v>1500000</v>
+        <v>300000</v>
       </c>
       <c r="H18" s="13" t="n">
         <f aca="false">F18*G18</f>
-        <v>1500000</v>
-      </c>
-      <c r="I18" s="23" t="s">
-        <v>111</v>
-      </c>
+        <v>900000</v>
+      </c>
+      <c r="I18" s="23"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" s="22" t="n">
-        <v>500000</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G19" s="13"/>
       <c r="H19" s="13" t="n">
-        <f aca="false">F19*G19</f>
-        <v>1500000</v>
-      </c>
-      <c r="I19" s="23"/>
+        <f aca="false">(H14)*0.033</f>
+        <v>118800</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D20" s="11"/>
-      <c r="E20" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G20" s="13"/>
+      <c r="E20" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="22" t="n">
+        <v>543417</v>
+      </c>
       <c r="H20" s="13" t="n">
-        <f aca="false">(H12)*0.033</f>
-        <v>118800</v>
+        <f aca="false">F20*G20</f>
+        <v>543417</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="22" t="n">
-        <v>1256100</v>
-      </c>
-      <c r="H21" s="13" t="n">
-        <f aca="false">F21*G21</f>
-        <v>1256100</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>63</v>
-      </c>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="16" t="n">
+        <f aca="false">SUM(H11:H20)</f>
+        <v>18000000</v>
+      </c>
+      <c r="I21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="19"/>
+      <c r="A22" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
       <c r="H22" s="16" t="n">
-        <f aca="false">SUM(H11:H21)</f>
+        <f aca="false">H21</f>
         <v>18000000</v>
       </c>
       <c r="I22" s="17"/>
     </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16" t="n">
-        <f aca="false">H22</f>
-        <v>18000000</v>
-      </c>
-      <c r="I23" s="17"/>
+    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -6168,7 +6656,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -6179,26 +6667,13 @@
       <c r="H26" s="20"/>
       <c r="I26" s="20"/>
     </row>
-    <row r="27" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="26" t="s">
         <v>65</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="G4:I4"/>
@@ -6206,13 +6681,14 @@
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:B17"/>
-    <mergeCell ref="A18:B21"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="A11:B13"/>
+    <mergeCell ref="A14:B17"/>
+    <mergeCell ref="A18:B20"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="A24:I24"/>
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A27:I27"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6229,6 +6705,193 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="29" t="n">
+        <f aca="false">A4*B4</f>
+        <v>40</v>
+      </c>
+      <c r="D4" s="28" t="n">
+        <v>72.4</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <f aca="false">C4*D4</f>
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" s="29" t="n">
+        <f aca="false">A5*B5</f>
+        <v>80</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>72.4</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <f aca="false">C5*D5</f>
+        <v>5792</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B6" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <f aca="false">A6*B6</f>
+        <v>18</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>72.4</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <f aca="false">C6*D6</f>
+        <v>1303.2</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="31"/>
+      <c r="B7" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <f aca="false">SUM(C4:C6)</f>
+        <v>138</v>
+      </c>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32" t="n">
+        <f aca="false">SUM(E4:E6)</f>
+        <v>9991.2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="36" t="n">
+        <v>13575440</v>
+      </c>
+      <c r="C10" s="37" t="n">
+        <f aca="false">B10/$E$7</f>
+        <v>1358.73969092802</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>9577783</v>
+      </c>
+      <c r="C11" s="37" t="n">
+        <f aca="false">B11/$E$7</f>
+        <v>958.621887260789</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="36" t="n">
+        <v>160000</v>
+      </c>
+      <c r="C12" s="35"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" s="36" t="n">
+        <v>600000</v>
+      </c>
+      <c r="C13" s="35"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" s="39" t="n">
+        <f aca="false">B10-B11</f>
+        <v>3997657</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="26" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -6238,149 +6901,149 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
-        <v>112</v>
+      <c r="A1" s="40" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>114</v>
+      <c r="A3" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>127</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
+      <c r="A4" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="31"/>
+      <c r="A5" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
+      <c r="A6" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
+      <c r="A7" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
+      <c r="A8" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v2.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v2.xlsx
@@ -25,12 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="150">
   <si>
     <t xml:space="preserve">견      적      서</t>
   </si>
   <si>
-    <t xml:space="preserve"> 금강변압기 귀하</t>
+    <t xml:space="preserve"> 금강변압기 유한회사 귀하</t>
   </si>
   <si>
     <t xml:space="preserve">엔엠솔루션</t>
@@ -120,6 +120,93 @@
   <si>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">   공사 장소 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경기 화성시 마도면 마도공단로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">길 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">214 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금강변압기 유한회사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(KUMKANG TRANSFORMER) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">마당</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF000000"/>
@@ -147,7 +234,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">금강변압기 마당 진공건조로 </t>
+      <t xml:space="preserve">금강변압기 유한회사 마당 진공건조로 </t>
     </r>
     <r>
       <rPr>
@@ -4944,9 +5031,22 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -4959,7 +5059,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -4972,40 +5072,40 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>1</v>
@@ -5019,20 +5119,20 @@
         <v>20000000</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>1</v>
@@ -5046,20 +5146,20 @@
         <v>25000000</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>1</v>
@@ -5073,18 +5173,18 @@
         <v>18000000</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
@@ -5096,7 +5196,7 @@
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -5112,13 +5212,13 @@
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -5130,7 +5230,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
@@ -5143,7 +5243,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
@@ -5156,7 +5256,7 @@
     </row>
     <row r="21" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -5169,7 +5269,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
@@ -5182,7 +5282,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
@@ -5194,12 +5294,13 @@
       <c r="I23" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="A11:C11"/>
@@ -5298,9 +5399,22 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -5313,42 +5427,42 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F11" s="21" t="n">
         <v>21</v>
@@ -5361,20 +5475,20 @@
         <v>6300000</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F12" s="21" t="n">
         <v>3</v>
@@ -5387,20 +5501,20 @@
         <v>1050000</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F13" s="21" t="n">
         <v>1</v>
@@ -5413,20 +5527,20 @@
         <v>2400000</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" s="21" t="n">
         <v>1</v>
@@ -5439,20 +5553,20 @@
         <v>1700000</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15" s="21" t="n">
         <v>1</v>
@@ -5465,20 +5579,20 @@
         <v>2000000</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F16" s="21" t="n">
         <v>1</v>
@@ -5496,11 +5610,11 @@
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F17" s="21" t="n">
         <v>3</v>
@@ -5516,15 +5630,15 @@
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18" s="21" t="n">
         <v>1</v>
@@ -5542,11 +5656,11 @@
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F19" s="24" t="n">
         <v>3.3</v>
@@ -5557,18 +5671,18 @@
         <v>242550</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" s="21" t="n">
         <v>1</v>
@@ -5581,14 +5695,14 @@
         <v>707450</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18"/>
       <c r="B21" s="18"/>
       <c r="C21" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
@@ -5602,13 +5716,13 @@
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
@@ -5620,7 +5734,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -5633,7 +5747,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -5646,7 +5760,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -5659,16 +5773,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:B17"/>
@@ -5760,9 +5875,22 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -5775,42 +5903,42 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F11" s="21" t="n">
         <v>9</v>
@@ -5823,20 +5951,20 @@
         <v>3150000</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F12" s="21" t="n">
         <v>6</v>
@@ -5849,22 +5977,22 @@
         <v>2700000</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" s="21" t="n">
         <v>4</v>
@@ -5877,20 +6005,20 @@
         <v>1200000</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="21" t="n">
         <v>4</v>
@@ -5903,22 +6031,22 @@
         <v>800000</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" s="21" t="n">
         <v>5</v>
@@ -5931,20 +6059,20 @@
         <v>1500000</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F16" s="21" t="n">
         <v>9</v>
@@ -5957,20 +6085,20 @@
         <v>3600000</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F17" s="21" t="n">
         <v>1</v>
@@ -5988,13 +6116,13 @@
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18" s="21" t="n">
         <v>1</v>
@@ -6012,13 +6140,13 @@
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F19" s="21" t="n">
         <v>1</v>
@@ -6031,20 +6159,20 @@
         <v>2500000</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" s="21" t="n">
         <v>1</v>
@@ -6060,15 +6188,15 @@
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F21" s="21" t="n">
         <v>5</v>
@@ -6086,11 +6214,11 @@
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
       <c r="C22" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F22" s="24" t="n">
         <v>3.3</v>
@@ -6101,18 +6229,18 @@
         <v>308550</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F23" s="21" t="n">
         <v>1</v>
@@ -6125,14 +6253,14 @@
         <v>941450</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="18"/>
       <c r="B24" s="18"/>
       <c r="C24" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="18"/>
@@ -6146,13 +6274,13 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
@@ -6164,7 +6292,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -6177,7 +6305,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -6190,7 +6318,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
@@ -6203,16 +6331,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:B12"/>
@@ -6306,9 +6435,22 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -6321,42 +6463,42 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" s="21" t="n">
         <v>1</v>
@@ -6369,20 +6511,20 @@
         <v>9577783</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" s="21" t="n">
         <v>1</v>
@@ -6395,20 +6537,20 @@
         <v>160000</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F13" s="21" t="n">
         <v>2</v>
@@ -6424,17 +6566,17 @@
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="21" t="n">
         <v>12</v>
@@ -6447,20 +6589,20 @@
         <v>3600000</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15" s="21" t="n">
         <v>1</v>
@@ -6478,13 +6620,13 @@
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F16" s="21" t="n">
         <v>1</v>
@@ -6502,13 +6644,13 @@
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F17" s="21" t="n">
         <v>1</v>
@@ -6521,20 +6663,20 @@
         <v>500000</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F18" s="21" t="n">
         <v>3</v>
@@ -6552,11 +6694,11 @@
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F19" s="24" t="n">
         <v>3.3</v>
@@ -6567,18 +6709,18 @@
         <v>118800</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" s="21" t="n">
         <v>1</v>
@@ -6591,14 +6733,14 @@
         <v>543417</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18"/>
       <c r="B21" s="18"/>
       <c r="C21" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
@@ -6612,13 +6754,13 @@
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
@@ -6630,7 +6772,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -6643,7 +6785,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -6656,7 +6798,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -6669,16 +6811,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:B13"/>
@@ -6717,24 +6860,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6797,7 +6940,7 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31"/>
       <c r="B7" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" s="31" t="n">
         <f aca="false">SUM(C4:C6)</f>
@@ -6811,18 +6954,18 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B10" s="36" t="n">
         <v>13575440</v>
@@ -6834,7 +6977,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B11" s="36" t="n">
         <v>9577783</v>
@@ -6846,7 +6989,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B12" s="36" t="n">
         <v>160000</v>
@@ -6855,7 +6998,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B13" s="36" t="n">
         <v>600000</v>
@@ -6864,7 +7007,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="38" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B14" s="39" t="n">
         <f aca="false">B10-B11</f>
@@ -6873,7 +7016,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -6902,56 +7045,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C4" s="43"/>
       <c r="D4" s="43"/>
@@ -6967,10 +7110,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
@@ -6986,10 +7129,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C6" s="35"/>
       <c r="D6" s="35"/>
@@ -7005,10 +7148,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
@@ -7024,10 +7167,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C8" s="35"/>
       <c r="D8" s="35"/>
@@ -7043,7 +7186,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v2.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v2.xlsx
@@ -9,11 +9,12 @@
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="도비" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="용접" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="베이스" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="베이스자재" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="공정표" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="산출근거" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="도비" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="용접" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="베이스" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="베이스자재" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="공정표" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="195">
   <si>
     <t xml:space="preserve">견      적      서</t>
   </si>
@@ -1316,6 +1317,2512 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">견적 산출근거</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금액은 공종 시트에서 연동돼요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">초록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">근거가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가정값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인 항목은 단가를 받으면 바꿀 수 있어요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">공종</t>
+  </si>
+  <si>
+    <t xml:space="preserve">항목</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">규격</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내용</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">산출식</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금액</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">근거</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인건비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도비 전문기공</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 300,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인원 가정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일수 사용자 제시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단가 서해테크 도비 견적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10.10) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단가</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">안전관리자</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 350,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가정값 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">크 레 인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100TON</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 2,400,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">사용자 제시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60TON</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 1,700,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">밀착 장비</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유압잭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">윈치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스키드</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">식 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">밀착 이동 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">공구사용손료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도비전문장비</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">식</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서해테크 도비 견적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10.10) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단가</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">일반관리비</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 700,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">소모품잡자재</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">산재보험</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인건비 합계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3.3%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">원가 계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">견적 금액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사용자 제시 공종 금액</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기업이윤 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">견적 − 원가</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">이윤율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">용접</t>
+  </si>
+  <si>
+    <t xml:space="preserve">용접사</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 350,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일수 사용자 제시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일당 가정값 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">고급기술자</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 450,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">사상 기술자</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 300,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일수 사용자 제시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일당 서해테크 도비 견적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10.10) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단가 전문기공 준용</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">조공</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 200,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안전관리자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화기감시</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 300,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">장비 대여</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CO2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용접기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 400,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">장비사용료</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그라인더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">환기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조명</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">재료비</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CO2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">와이어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디스크</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">비파괴검사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PT/UT</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">식 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요구 시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">도장 보수</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">용접부</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 600,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가정값 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서해테크 방식 준용</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">베이스</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빔 구매 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">H-250×250, 10m 4EA·5m 16EA·0.6m 30EA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중고 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">식 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">신품 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13,575,440</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급처 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빔 견적 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부가세 별도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">운임</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빔 운반</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급처 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빔 견적</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">지 게 차</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자재 하역</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조립</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 300,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">제작 기공</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 300,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용접기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">절단기</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">소모품</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용접봉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디스크</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">슬라이딩면 처리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그리스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·PTFE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시트</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 300,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">근거 구분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 제시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">받은 단가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서해테크 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">도비 협력사 견적서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-10) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급처 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빔 견적 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가정값 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제가 넣은 값</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -1468,12 +3975,6 @@
     <t xml:space="preserve">기계작업</t>
   </si>
   <si>
-    <t xml:space="preserve">인건비</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도비 전문기공</t>
-  </si>
-  <si>
     <t xml:space="preserve">M</t>
   </si>
   <si>
@@ -1603,9 +4104,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">안전관리자</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1627,12 +4125,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">크 레 인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100TON</t>
-  </si>
-  <si>
     <t xml:space="preserve">대</t>
   </si>
   <si>
@@ -1704,9 +4196,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">60TON</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1775,58 +4264,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">밀착 장비</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">유압잭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">윈치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">스키드</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">SET</t>
   </si>
   <si>
@@ -1860,54 +4297,12 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">공구사용손료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도비전문장비</t>
-  </si>
-  <si>
-    <t xml:space="preserve">일반관리비</t>
-  </si>
-  <si>
     <t xml:space="preserve">DAY</t>
   </si>
   <si>
     <t xml:space="preserve">기타비용</t>
   </si>
   <si>
-    <t xml:space="preserve">소모품잡자재</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">고용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&amp;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">산재보험</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">%</t>
   </si>
   <si>
@@ -1935,7 +4330,44 @@
     <t xml:space="preserve">기업이윤</t>
   </si>
   <si>
-    <t xml:space="preserve">목표 금액 맞춤 조정 항목</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">견적 금액 − 원가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">산출근거 시트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">소    계</t>
@@ -2167,9 +4599,6 @@
     <t xml:space="preserve">용접작업</t>
   </si>
   <si>
-    <t xml:space="preserve">용접사</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2210,9 +4639,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">고급기술자</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2256,9 +4682,6 @@
     <t xml:space="preserve">사상작업</t>
   </si>
   <si>
-    <t xml:space="preserve">사상 기술자</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2299,17 +4722,82 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">조공</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전관리자</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사상 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용접 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
     </r>
     <r>
       <rPr>
@@ -2328,57 +4816,10 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">화기감시</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사상 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">용접 </t>
-    </r>
+      <t xml:space="preserve">일</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2396,46 +4837,132 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">일</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">장비 대여</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CO2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">용접기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대당 일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요구 시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">범위 확인 필요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  작업 내용</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사다리형 일체 베이스 제작</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
@@ -2445,33 +4972,148 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설치</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, H-250×250 (4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">일</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대 </t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">자재</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급처 견적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">신품 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13,575,440</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">공급처 견적</t>
+  </si>
+  <si>
+    <t xml:space="preserve">일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제작작업</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
     </r>
     <r>
       <rPr>
@@ -2492,9 +5134,67 @@
       </rPr>
       <t xml:space="preserve">일</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+  </si>
+  <si>
+    <t xml:space="preserve">밀착 이동용 레일 상면</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">베이스 자재</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: H</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빔 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H-250×250×9×14 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급처 견적</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
@@ -2504,315 +5204,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대당 일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만 원</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">장비사용료</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그라인더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">환기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조명</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">재료비</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CO2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">와이어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">디스크</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">비파괴검사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT/UT</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요구 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">범위 확인 필요</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방청</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">도장 보수</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">용접부</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  작업 내용</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사다리형 일체 베이스 제작</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">설치</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, H-250×250 (4</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부가세 미포함</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
@@ -2822,424 +5225,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">자재</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빔 구매 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">H-250×250, 10m 4EA·5m 16EA·0.6m 30EA</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">공급처 견적</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">신품 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13,575,440</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">운임</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빔 운반</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">공급처 견적</t>
-  </si>
-  <si>
-    <t xml:space="preserve">지 게 차</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자재 하역</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조립</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">일</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제작작업</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제작 기공</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">용접기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">절단기</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">소모품</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">용접봉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">디스크</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">슬라이딩면 처리</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그리스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·PTFE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시트</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">밀착 이동용 레일 상면</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">베이스 자재</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: H</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빔 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H-250×250×9×14 (</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">공급처 견적</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부가세 미포함</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -3356,50 +5341,6 @@
   </si>
   <si>
     <t xml:space="preserve">합계</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금액</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -4292,14 +6233,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="General"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4411,6 +6353,14 @@
       <color rgb="FF000000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4536,7 +6486,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="53">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4621,43 +6571,79 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4665,7 +6651,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4677,19 +6663,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4697,7 +6683,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5333,6 +7319,819 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="24" t="n">
+        <f aca="false">도비!H11</f>
+        <v>6300000</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <f aca="false">도비!H12</f>
+        <v>1050000</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <f aca="false">도비!H13</f>
+        <v>2400000</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <f aca="false">도비!H14</f>
+        <v>1700000</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="24" t="n">
+        <f aca="false">도비!H15</f>
+        <v>2000000</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="24" t="n">
+        <f aca="false">도비!H16</f>
+        <v>3000000</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="23"/>
+      <c r="D11" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="24" t="n">
+        <f aca="false">도비!H17</f>
+        <v>2100000</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="23"/>
+      <c r="D12" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <f aca="false">도비!H18</f>
+        <v>1000000</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <f aca="false">도비!H19</f>
+        <v>242550</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17"/>
+      <c r="B14" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="27" t="n">
+        <f aca="false">SUM(E5:E13)</f>
+        <v>19792550</v>
+      </c>
+      <c r="F14" s="17"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17"/>
+      <c r="B15" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="28" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29"/>
+      <c r="B16" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="27" t="n">
+        <f aca="false">E15-E14</f>
+        <v>207450</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <f aca="false">E16/E14</f>
+        <v>0.0104812164172883</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <f aca="false">용접!H11</f>
+        <v>3150000</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <f aca="false">용접!H12</f>
+        <v>2700000</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <f aca="false">용접!H13</f>
+        <v>1200000</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="24" t="n">
+        <f aca="false">용접!H14</f>
+        <v>800000</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <f aca="false">용접!H15</f>
+        <v>1500000</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="24" t="n">
+        <f aca="false">용접!H16</f>
+        <v>3600000</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <f aca="false">용접!H17</f>
+        <v>800000</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="24" t="n">
+        <f aca="false">용접!H18</f>
+        <v>3000000</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E26" s="24" t="n">
+        <f aca="false">용접!H19</f>
+        <v>2500000</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="24" t="n">
+        <f aca="false">용접!H20</f>
+        <v>1500000</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="23"/>
+      <c r="D28" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="24" t="n">
+        <f aca="false">용접!H21</f>
+        <v>3000000</v>
+      </c>
+      <c r="F28" s="25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="24" t="n">
+        <f aca="false">용접!H22</f>
+        <v>308550</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="29"/>
+      <c r="B30" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="27" t="n">
+        <f aca="false">SUM(E18:E29)</f>
+        <v>24058550</v>
+      </c>
+      <c r="F30" s="29"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="29"/>
+      <c r="B31" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="28" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="F31" s="29" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="29"/>
+      <c r="B32" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="27" t="n">
+        <f aca="false">E31-E30</f>
+        <v>941450</v>
+      </c>
+      <c r="F32" s="30" t="n">
+        <f aca="false">E32/E30</f>
+        <v>0.0391316184890611</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" s="24" t="n">
+        <f aca="false">베이스!H11</f>
+        <v>9577783</v>
+      </c>
+      <c r="F34" s="23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E35" s="24" t="n">
+        <f aca="false">베이스!H12</f>
+        <v>160000</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E36" s="24" t="n">
+        <f aca="false">베이스!H13</f>
+        <v>600000</v>
+      </c>
+      <c r="F36" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E37" s="24" t="n">
+        <f aca="false">베이스!H14</f>
+        <v>3600000</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E38" s="24" t="n">
+        <f aca="false">베이스!H15</f>
+        <v>1000000</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" s="24" t="n">
+        <f aca="false">베이스!H16</f>
+        <v>1000000</v>
+      </c>
+      <c r="F39" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E40" s="24" t="n">
+        <f aca="false">베이스!H17</f>
+        <v>500000</v>
+      </c>
+      <c r="F40" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="23"/>
+      <c r="D41" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="E41" s="24" t="n">
+        <f aca="false">베이스!H18</f>
+        <v>900000</v>
+      </c>
+      <c r="F41" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="24" t="n">
+        <f aca="false">베이스!H19</f>
+        <v>118800</v>
+      </c>
+      <c r="F42" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="29"/>
+      <c r="B43" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="27" t="n">
+        <f aca="false">SUM(E34:E42)</f>
+        <v>17456583</v>
+      </c>
+      <c r="F43" s="29"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="29"/>
+      <c r="B44" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="28" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="F44" s="29" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="29"/>
+      <c r="B45" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E45" s="27" t="n">
+        <f aca="false">E44-E43</f>
+        <v>543417</v>
+      </c>
+      <c r="F45" s="30" t="n">
+        <f aca="false">E45/E43</f>
+        <v>0.0311296317268964</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -5414,7 +8213,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -5452,22 +8251,22 @@
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="21" t="n">
+        <v>124</v>
+      </c>
+      <c r="F11" s="31" t="n">
         <v>21</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="32" t="n">
         <v>300000</v>
       </c>
       <c r="H11" s="13" t="n">
@@ -5475,25 +8274,25 @@
         <v>6300000</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="21" t="n">
+        <v>124</v>
+      </c>
+      <c r="F12" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="32" t="n">
         <v>350000</v>
       </c>
       <c r="H12" s="13" t="n">
@@ -5501,25 +8300,25 @@
         <v>1050000</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="21" t="n">
+        <v>127</v>
+      </c>
+      <c r="F13" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="32" t="n">
         <v>2400000</v>
       </c>
       <c r="H13" s="13" t="n">
@@ -5527,25 +8326,25 @@
         <v>2400000</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>47</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="21" t="n">
+        <v>127</v>
+      </c>
+      <c r="F14" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="32" t="n">
         <v>1700000</v>
       </c>
       <c r="H14" s="13" t="n">
@@ -5553,25 +8352,25 @@
         <v>1700000</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="21" t="n">
+        <v>130</v>
+      </c>
+      <c r="F15" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="32" t="n">
         <v>2000000</v>
       </c>
       <c r="H15" s="13" t="n">
@@ -5579,30 +8378,30 @@
         <v>2000000</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="21" t="n">
+        <v>130</v>
+      </c>
+      <c r="F16" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="22" t="n">
-        <v>2500000</v>
+      <c r="G16" s="32" t="n">
+        <v>3000000</v>
       </c>
       <c r="H16" s="13" t="n">
         <f aca="false">F16*G16</f>
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="I16" s="23"/>
     </row>
@@ -5610,16 +8409,16 @@
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="21" t="n">
+        <v>132</v>
+      </c>
+      <c r="F17" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="22" t="n">
+      <c r="G17" s="32" t="n">
         <v>700000</v>
       </c>
       <c r="H17" s="13" t="n">
@@ -5630,20 +8429,20 @@
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="21" t="n">
+      <c r="F18" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="22" t="n">
+      <c r="G18" s="32" t="n">
         <v>1000000</v>
       </c>
       <c r="H18" s="13" t="n">
@@ -5656,13 +8455,13 @@
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="24" t="n">
+        <v>134</v>
+      </c>
+      <c r="F19" s="33" t="n">
         <v>3.3</v>
       </c>
       <c r="G19" s="13"/>
@@ -5671,48 +8470,48 @@
         <v>242550</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="21" t="n">
+      <c r="F20" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="22" t="n">
-        <v>707450</v>
+      <c r="G20" s="32" t="n">
+        <v>207450</v>
       </c>
       <c r="H20" s="13" t="n">
         <f aca="false">F20*G20</f>
-        <v>707450</v>
+        <v>207450</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18"/>
       <c r="B21" s="18"/>
       <c r="C21" s="9" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
-      <c r="F21" s="25"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="19"/>
       <c r="H21" s="16" t="n">
         <f aca="false">SUM(H11:H20)</f>
         <v>20000000</v>
       </c>
-      <c r="I21" s="17"/>
+      <c r="I21" s="29"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
@@ -5730,7 +8529,7 @@
         <f aca="false">H21</f>
         <v>20000000</v>
       </c>
-      <c r="I22" s="17"/>
+      <c r="I22" s="29"/>
     </row>
     <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
@@ -5772,8 +8571,8 @@
       <c r="I26" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="26" t="s">
-        <v>66</v>
+      <c r="A28" s="35" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -5804,7 +8603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -5890,7 +8689,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>67</v>
+        <v>140</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -5928,22 +8727,22 @@
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="21" t="n">
+        <v>124</v>
+      </c>
+      <c r="F11" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="32" t="n">
         <v>350000</v>
       </c>
       <c r="H11" s="13" t="n">
@@ -5951,25 +8750,25 @@
         <v>3150000</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>70</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="21" t="n">
+        <v>124</v>
+      </c>
+      <c r="F12" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="32" t="n">
         <v>450000</v>
       </c>
       <c r="H12" s="13" t="n">
@@ -5977,27 +8776,27 @@
         <v>2700000</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="21" t="n">
+        <v>124</v>
+      </c>
+      <c r="F13" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="32" t="n">
         <v>300000</v>
       </c>
       <c r="H13" s="13" t="n">
@@ -6005,25 +8804,25 @@
         <v>1200000</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="21" t="n">
+        <v>124</v>
+      </c>
+      <c r="F14" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="32" t="n">
         <v>200000</v>
       </c>
       <c r="H14" s="13" t="n">
@@ -6031,27 +8830,27 @@
         <v>800000</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="21" t="n">
+        <v>124</v>
+      </c>
+      <c r="F15" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="32" t="n">
         <v>300000</v>
       </c>
       <c r="H15" s="13" t="n">
@@ -6059,25 +8858,25 @@
         <v>1500000</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>78</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F16" s="21" t="n">
+        <v>147</v>
+      </c>
+      <c r="F16" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="32" t="n">
         <v>400000</v>
       </c>
       <c r="H16" s="13" t="n">
@@ -6085,25 +8884,25 @@
         <v>3600000</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>82</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="21" t="n">
+        <v>130</v>
+      </c>
+      <c r="F17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="22" t="n">
+      <c r="G17" s="32" t="n">
         <v>800000</v>
       </c>
       <c r="H17" s="13" t="n">
@@ -6116,18 +8915,18 @@
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="21" t="n">
+      <c r="F18" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="22" t="n">
+      <c r="G18" s="32" t="n">
         <v>3000000</v>
       </c>
       <c r="H18" s="13" t="n">
@@ -6140,18 +8939,18 @@
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="F19" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="22" t="n">
+      <c r="G19" s="32" t="n">
         <v>2500000</v>
       </c>
       <c r="H19" s="13" t="n">
@@ -6159,25 +8958,25 @@
         <v>2500000</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="21" t="n">
+      <c r="F20" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="22" t="n">
+      <c r="G20" s="32" t="n">
         <v>1500000</v>
       </c>
       <c r="H20" s="13" t="n">
@@ -6188,20 +8987,20 @@
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" s="21" t="n">
+        <v>132</v>
+      </c>
+      <c r="F21" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="G21" s="22" t="n">
+      <c r="G21" s="32" t="n">
         <v>600000</v>
       </c>
       <c r="H21" s="13" t="n">
@@ -6214,13 +9013,13 @@
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
       <c r="C22" s="11" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F22" s="24" t="n">
+        <v>134</v>
+      </c>
+      <c r="F22" s="33" t="n">
         <v>3.3</v>
       </c>
       <c r="G22" s="13"/>
@@ -6229,23 +9028,23 @@
         <v>308550</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="21" t="n">
+      <c r="F23" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="22" t="n">
+      <c r="G23" s="32" t="n">
         <v>941450</v>
       </c>
       <c r="H23" s="13" t="n">
@@ -6253,24 +9052,24 @@
         <v>941450</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="18"/>
       <c r="B24" s="18"/>
       <c r="C24" s="9" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="18"/>
-      <c r="F24" s="25"/>
+      <c r="F24" s="34"/>
       <c r="G24" s="19"/>
       <c r="H24" s="16" t="n">
         <f aca="false">SUM(H11:H23)</f>
         <v>25000000</v>
       </c>
-      <c r="I24" s="17"/>
+      <c r="I24" s="29"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
@@ -6288,7 +9087,7 @@
         <f aca="false">H24</f>
         <v>25000000</v>
       </c>
-      <c r="I25" s="17"/>
+      <c r="I25" s="29"/>
     </row>
     <row r="27" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
@@ -6330,8 +9129,8 @@
       <c r="I29" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="26" t="s">
-        <v>66</v>
+      <c r="A31" s="35" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -6364,7 +9163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -6450,7 +9249,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -6488,22 +9287,22 @@
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="10" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="F11" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="32" t="n">
         <v>9577783</v>
       </c>
       <c r="H11" s="13" t="n">
@@ -6511,25 +9310,25 @@
         <v>9577783</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="32" t="n">
         <v>160000</v>
       </c>
       <c r="H12" s="13" t="n">
@@ -6537,25 +9336,25 @@
         <v>160000</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>99</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F13" s="21" t="n">
+        <v>154</v>
+      </c>
+      <c r="F13" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="32" t="n">
         <v>300000</v>
       </c>
       <c r="H13" s="13" t="n">
@@ -6566,22 +9365,22 @@
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="21" t="n">
+        <v>124</v>
+      </c>
+      <c r="F14" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="32" t="n">
         <v>300000</v>
       </c>
       <c r="H14" s="13" t="n">
@@ -6589,25 +9388,25 @@
         <v>3600000</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="21" t="n">
+        <v>130</v>
+      </c>
+      <c r="F15" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="32" t="n">
         <v>1000000</v>
       </c>
       <c r="H15" s="13" t="n">
@@ -6620,18 +9419,18 @@
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="21" t="n">
+      <c r="F16" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="32" t="n">
         <v>1000000</v>
       </c>
       <c r="H16" s="13" t="n">
@@ -6644,18 +9443,18 @@
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="21" t="n">
+      <c r="F17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="22" t="n">
+      <c r="G17" s="32" t="n">
         <v>500000</v>
       </c>
       <c r="H17" s="13" t="n">
@@ -6663,25 +9462,25 @@
         <v>500000</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="21" t="n">
+        <v>132</v>
+      </c>
+      <c r="F18" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="22" t="n">
+      <c r="G18" s="32" t="n">
         <v>300000</v>
       </c>
       <c r="H18" s="13" t="n">
@@ -6694,13 +9493,13 @@
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="24" t="n">
+        <v>134</v>
+      </c>
+      <c r="F19" s="33" t="n">
         <v>3.3</v>
       </c>
       <c r="G19" s="13"/>
@@ -6709,23 +9508,23 @@
         <v>118800</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="21" t="n">
+      <c r="F20" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="22" t="n">
+      <c r="G20" s="32" t="n">
         <v>543417</v>
       </c>
       <c r="H20" s="13" t="n">
@@ -6733,24 +9532,24 @@
         <v>543417</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18"/>
       <c r="B21" s="18"/>
       <c r="C21" s="9" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
-      <c r="F21" s="25"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="19"/>
       <c r="H21" s="16" t="n">
         <f aca="false">SUM(H11:H20)</f>
         <v>18000000</v>
       </c>
-      <c r="I21" s="17"/>
+      <c r="I21" s="29"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
@@ -6768,7 +9567,7 @@
         <f aca="false">H21</f>
         <v>18000000</v>
       </c>
-      <c r="I22" s="17"/>
+      <c r="I22" s="29"/>
     </row>
     <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
@@ -6810,8 +9609,8 @@
       <c r="I26" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="26" t="s">
-        <v>66</v>
+      <c r="A28" s="35" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -6843,7 +9642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -6859,164 +9658,164 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
-        <v>112</v>
+      <c r="A1" s="36" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>115</v>
+        <v>161</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="n">
+      <c r="A4" s="37" t="n">
         <v>10</v>
       </c>
-      <c r="B4" s="28" t="n">
+      <c r="B4" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="38" t="n">
         <f aca="false">A4*B4</f>
         <v>40</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="37" t="n">
         <v>72.4</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="39" t="n">
         <f aca="false">C4*D4</f>
         <v>2896</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="B5" s="28" t="n">
+      <c r="B5" s="37" t="n">
         <v>16</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="38" t="n">
         <f aca="false">A5*B5</f>
         <v>80</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="37" t="n">
         <v>72.4</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="39" t="n">
         <f aca="false">C5*D5</f>
         <v>5792</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="n">
+      <c r="A6" s="37" t="n">
         <v>0.6</v>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="37" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="38" t="n">
         <f aca="false">A6*B6</f>
         <v>18</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="37" t="n">
         <v>72.4</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="39" t="n">
         <f aca="false">C6*D6</f>
         <v>1303.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31"/>
+      <c r="A7" s="40"/>
       <c r="B7" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="31" t="n">
+        <v>164</v>
+      </c>
+      <c r="C7" s="40" t="n">
         <f aca="false">SUM(C4:C6)</f>
         <v>138</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="32" t="n">
+      <c r="D7" s="40"/>
+      <c r="E7" s="41" t="n">
         <f aca="false">SUM(E4:E6)</f>
         <v>9991.2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>120</v>
+      <c r="B9" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="B10" s="36" t="n">
+      <c r="A10" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="45" t="n">
         <v>13575440</v>
       </c>
-      <c r="C10" s="37" t="n">
+      <c r="C10" s="46" t="n">
         <f aca="false">B10/$E$7</f>
         <v>1358.73969092802</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="36" t="n">
+      <c r="A11" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" s="45" t="n">
         <v>9577783</v>
       </c>
-      <c r="C11" s="37" t="n">
+      <c r="C11" s="46" t="n">
         <f aca="false">B11/$E$7</f>
         <v>958.621887260789</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="36" t="n">
+      <c r="A12" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="45" t="n">
         <v>160000</v>
       </c>
-      <c r="C12" s="35"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="B13" s="36" t="n">
+      <c r="A13" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" s="45" t="n">
         <v>600000</v>
       </c>
-      <c r="C13" s="35"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="B14" s="39" t="n">
+      <c r="A14" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="B14" s="48" t="n">
         <f aca="false">B10-B11</f>
         <v>3997657</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26" t="s">
-        <v>125</v>
+      <c r="A16" s="35" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -7030,7 +9829,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -7044,149 +9843,149 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
-        <v>126</v>
+      <c r="A1" s="49" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="41" t="s">
-        <v>127</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>128</v>
+      <c r="A3" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>173</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>139</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
+      <c r="A4" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
+      <c r="A5" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" s="51" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
+      <c r="A6" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="B7" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
+      <c r="A7" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="B8" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
+      <c r="A8" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
-        <v>149</v>
+      <c r="A10" s="35" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
